--- a/03_Cluster_groups/Muscle_size/01_Clustering/c_data/clustering.xlsx
+++ b/03_Cluster_groups/Muscle_size/01_Clustering/c_data/clustering.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="277">
   <si>
     <t>sheet</t>
   </si>
@@ -46,7 +46,7 @@
     <t>diagnostics</t>
   </si>
   <si>
-    <t>Per K: gap, SE, mean silhouette, group sizes, bootstrap Jaccard per cluster.</t>
+    <t>Per K: gap, SE, mean silhouette, group sizes, HR/LR adjusted Rand index, bootstrap Jaccard.</t>
   </si>
   <si>
     <t>stability</t>
@@ -181,6 +181,12 @@
     <t>People per cluster.</t>
   </si>
   <si>
+    <t>hr_lr_ari</t>
+  </si>
+  <si>
+    <t>Adjusted Rand index of the clustering against HR/LR.</t>
+  </si>
+  <si>
     <t>min_jaccard</t>
   </si>
   <si>
@@ -389,6 +395,51 @@
   </si>
   <si>
     <t>5a1989db406daa0b70189a9f0df52cf3</t>
+  </si>
+  <si>
+    <t>proteins</t>
+  </si>
+  <si>
+    <t>01_Trunk/03_Quantification/c_data/proteins.rds</t>
+  </si>
+  <si>
+    <t>34ef12f3ddbea70e6840925bab8692c5</t>
+  </si>
+  <si>
+    <t>DAList_corrected</t>
+  </si>
+  <si>
+    <t>01_Trunk/03_Quantification/c_data/DAList_corrected.rds</t>
+  </si>
+  <si>
+    <t>4b7147a39661ba7f9ed17b81a9ef9a9b</t>
+  </si>
+  <si>
+    <t>DAList_limpa</t>
+  </si>
+  <si>
+    <t>01_Trunk/03_Quantification/c_data/DAList_limpa.rds</t>
+  </si>
+  <si>
+    <t>268362b9975bc00d3bc3b85b0f5736f7</t>
+  </si>
+  <si>
+    <t>singscore</t>
+  </si>
+  <si>
+    <t>01_Trunk/05_Set_Scores/c_data/singscore.rds</t>
+  </si>
+  <si>
+    <t>4f1249d3e2d6782468d2836f84bdc76a</t>
+  </si>
+  <si>
+    <t>modules</t>
+  </si>
+  <si>
+    <t>01_Trunk/06_Module_Building/c_data/modules.rds</t>
+  </si>
+  <si>
+    <t>9062a97ff96fac52908895e0eeb7bf57</t>
   </si>
   <si>
     <t>BiocGenerics</t>
@@ -1240,772 +1291,772 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="B6" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="B8" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="B9" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="C13" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="C15" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B16" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="C16" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="B17" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="B18" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="B19" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="B20" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="B21" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="B22" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="B23" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="C23" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="B24" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B25" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="B26" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="B27" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="B28" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="B29" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="B30" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="B31" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="B32" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="B33" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="C33" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B34" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="B35" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="B36" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B37" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C37" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="B38" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C38" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="B39" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="B40" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B41" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C41" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="B42" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C42" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B43" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B44" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C44" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B45" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="C45" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B46" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C46" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="B47" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C47" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="B48" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C48" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B49" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C49" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="B50" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C50" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B51" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C51" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="B52" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="C52" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="B53" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="C53" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="B54" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="C54" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="B55" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C55" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="B56" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="C56" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="B57" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="C57" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="B58" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="C58" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="B59" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="C59" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="B60" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="C60" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="B61" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="C61" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="B62" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="C62" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="B63" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="C63" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="B64" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="C64" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="B65" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C65" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="B66" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C66" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="B67" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="C67" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="B68" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="C68" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="B69" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="C69" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="B70" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="C70" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2015,7 +2066,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -2218,13 +2269,13 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2232,10 +2283,10 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -2243,21 +2294,21 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2279,7 +2330,7 @@
         <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2287,10 +2338,10 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" t="s">
         <v>63</v>
-      </c>
-      <c r="C25" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2298,10 +2349,10 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2309,10 +2360,10 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2323,7 +2374,7 @@
         <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -2331,15 +2382,15 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B30" t="s">
         <v>58</v>
@@ -2353,10 +2404,10 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2397,21 +2448,21 @@
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2427,7 +2478,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B38" t="s">
         <v>80</v>
@@ -2460,7 +2511,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B41" t="s">
         <v>86</v>
@@ -2489,6 +2540,17 @@
       </c>
       <c r="C43" t="s">
         <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2529,13 +2591,13 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B2">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2544,7 +2606,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -2560,10 +2622,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1">
+    <row r="1" spans="1:10" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -2591,8 +2653,11 @@
       <c r="I1" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2609,7 +2674,7 @@
         <v>0.08979442721124117</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2629,16 +2694,19 @@
         <v>0.4379257616113116</v>
       </c>
       <c r="G3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>0.8788753968253967</v>
       </c>
-      <c r="I3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2658,13 +2726,16 @@
         <v>0.2748119581877786</v>
       </c>
       <c r="G4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H4">
+        <v>0.5392491467576792</v>
+      </c>
+      <c r="I4">
         <v>0.462647619047619</v>
       </c>
-      <c r="I4" t="s">
-        <v>98</v>
+      <c r="J4" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2682,10 +2753,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2755,33 +2826,33 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B2">
         <v>12.16232106959738</v>
@@ -2807,7 +2878,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B3">
         <v>31.80281346650556</v>
@@ -2833,7 +2904,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B4">
         <v>30.5494395516413</v>
@@ -2859,7 +2930,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5">
         <v>4.749681751727429</v>
@@ -2885,7 +2956,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6">
         <v>19.70296798862232</v>
@@ -2911,7 +2982,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B7">
         <v>23.02847460645439</v>
@@ -2937,7 +3008,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B8">
         <v>14.95445841883094</v>
@@ -2963,7 +3034,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B9">
         <v>-6.696894843631995</v>
@@ -2989,7 +3060,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B10">
         <v>-2.090289979057241</v>
@@ -3015,7 +3086,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B11">
         <v>17.27811743844548</v>
@@ -3041,7 +3112,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B12">
         <v>-17.35360011264369</v>
@@ -3067,7 +3138,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B13">
         <v>-4.547781417735207</v>
@@ -3093,7 +3164,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B14">
         <v>-30.66824655204562</v>
@@ -3119,7 +3190,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B15">
         <v>-21.58964552508842</v>
@@ -3145,7 +3216,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B16">
         <v>-31.46852200507816</v>
@@ -3171,7 +3242,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B17">
         <v>-21.03777027481851</v>
@@ -3207,33 +3278,33 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D2">
         <v>-0.9200264013847459</v>
@@ -3247,13 +3318,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D3">
         <v>-2.566276486720809</v>
@@ -3267,13 +3338,13 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D4">
         <v>-2.26960860624147</v>
@@ -3287,13 +3358,13 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D5">
         <v>-0.5212818663289102</v>
@@ -3307,13 +3378,13 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D6">
         <v>-1.629890077810509</v>
@@ -3327,13 +3398,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D7">
         <v>-1.765890108124135</v>
@@ -3347,13 +3418,13 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D8">
         <v>-1.104128876417801</v>
@@ -3367,13 +3438,13 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D9">
         <v>0.1490895154510403</v>
@@ -3387,13 +3458,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D10">
         <v>0.2486335312160351</v>
@@ -3407,13 +3478,13 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D11">
         <v>-0.8213747445579055</v>
@@ -3427,13 +3498,13 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D12">
         <v>1.588076749679427</v>
@@ -3447,13 +3518,13 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D13">
         <v>0.6569063970243449</v>
@@ -3467,13 +3538,13 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D14">
         <v>2.47858739522493</v>
@@ -3487,13 +3558,13 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D15">
         <v>1.946936877902724</v>
@@ -3507,13 +3578,13 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D16">
         <v>2.805905773949406</v>
@@ -3527,13 +3598,13 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D17">
         <v>1.72434092713838</v>
@@ -3557,15 +3628,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B2">
         <v>0.73903</v>
@@ -3573,7 +3644,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B3">
         <v>0.24328</v>
@@ -3586,29 +3657,84 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/03_Cluster_groups/Muscle_size/01_Clustering/c_data/clustering.xlsx
+++ b/03_Cluster_groups/Muscle_size/01_Clustering/c_data/clustering.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="258">
   <si>
     <t>sheet</t>
   </si>
@@ -238,7 +238,7 @@
     <t>arm</t>
   </si>
   <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster arc.</t>
+    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
   </si>
   <si>
     <t>group</t>
@@ -313,7 +313,7 @@
     <t>pct_fcsa_mixed, pct_fcsa_type1, pct_fcsa_type2, pct_mcsa</t>
   </si>
   <si>
-    <t>Gap statistic selects K = 1; K = 2 imposed by decision (2026-10-06). It reproduces the HR/LR split exactly, so this arc repeats that comparison under a size-cluster label.</t>
+    <t>Gap statistic selects K = 1; K = 2 imposed by decision (2026-10-06). It reproduces the HR/LR split exactly, so this grouping repeats that comparison under a size-cluster label.</t>
   </si>
   <si>
     <t>8/8</t>
@@ -397,51 +397,6 @@
     <t>5a1989db406daa0b70189a9f0df52cf3</t>
   </si>
   <si>
-    <t>proteins</t>
-  </si>
-  <si>
-    <t>01_Trunk/03_Quantification/c_data/proteins.rds</t>
-  </si>
-  <si>
-    <t>34ef12f3ddbea70e6840925bab8692c5</t>
-  </si>
-  <si>
-    <t>DAList_corrected</t>
-  </si>
-  <si>
-    <t>01_Trunk/03_Quantification/c_data/DAList_corrected.rds</t>
-  </si>
-  <si>
-    <t>4b7147a39661ba7f9ed17b81a9ef9a9b</t>
-  </si>
-  <si>
-    <t>DAList_limpa</t>
-  </si>
-  <si>
-    <t>01_Trunk/03_Quantification/c_data/DAList_limpa.rds</t>
-  </si>
-  <si>
-    <t>268362b9975bc00d3bc3b85b0f5736f7</t>
-  </si>
-  <si>
-    <t>singscore</t>
-  </si>
-  <si>
-    <t>01_Trunk/05_Set_Scores/c_data/singscore.rds</t>
-  </si>
-  <si>
-    <t>4f1249d3e2d6782468d2836f84bdc76a</t>
-  </si>
-  <si>
-    <t>modules</t>
-  </si>
-  <si>
-    <t>01_Trunk/06_Module_Building/c_data/modules.rds</t>
-  </si>
-  <si>
-    <t>9062a97ff96fac52908895e0eeb7bf57</t>
-  </si>
-  <si>
     <t>BiocGenerics</t>
   </si>
   <si>
@@ -661,12 +616,6 @@
     <t>1.0.5</t>
   </si>
   <si>
-    <t>limma</t>
-  </si>
-  <si>
-    <t>3.68.1</t>
-  </si>
-  <si>
     <t>magrittr</t>
   </si>
   <si>
@@ -809,12 +758,6 @@
   </si>
   <si>
     <t>1.4.6.1</t>
-  </si>
-  <si>
-    <t>statmod</t>
-  </si>
-  <si>
-    <t>1.5.1</t>
   </si>
   <si>
     <t>tibble</t>
@@ -1286,7 +1229,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -1302,90 +1245,90 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B7" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C7" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1393,670 +1336,648 @@
         <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="C10" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C11" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="B12" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="B13" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="B14" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="C14" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="B15" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="B16" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C16" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C17" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="B18" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C18" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="B19" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C19" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="B20" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="B21" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="C21" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="B22" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="C22" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="B23" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="C23" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="B24" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="B25" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="C25" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="B26" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="C26" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="C27" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="B28" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C28" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="C29" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="B30" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C30" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="B31" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C31" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="C32" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="B33" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="C33" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="B34" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="C34" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="B35" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="B36" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="C36" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B37" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="B38" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="C38" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="B39" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C39" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B40" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="B41" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="C41" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="B42" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="C42" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="B43" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="C43" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="C44" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="B45" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="C45" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="B46" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C46" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="B47" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C47" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="B48" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C48" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="B49" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="C49" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="B50" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="C50" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="B51" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="C51" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="B52" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="C52" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="B53" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="C53" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="B54" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="C54" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="B55" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C55" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="B56" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="C56" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B57" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="C57" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B58" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="C58" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="B59" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="C59" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="B60" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="C60" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="B61" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="C61" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="B62" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="C62" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="B63" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="C63" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="B64" t="s">
-        <v>265</v>
+        <v>161</v>
       </c>
       <c r="C64" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="B65" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="C65" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="B66" t="s">
-        <v>176</v>
+        <v>253</v>
       </c>
       <c r="C66" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="B67" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="C67" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="B68" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="C68" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
-        <v>273</v>
-      </c>
-      <c r="B69" t="s">
-        <v>274</v>
-      </c>
-      <c r="C69" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" t="s">
-        <v>275</v>
-      </c>
-      <c r="B70" t="s">
-        <v>276</v>
-      </c>
-      <c r="C70" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -3657,7 +3578,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -3682,61 +3603,6 @@
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C7" t="s">
-        <v>138</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
